--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2765,6 +2765,1892 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126057881</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>550014</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6942905</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126057604</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>550077</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6942975</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126057931</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56834</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>549950</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6942699</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning järpe.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126057541</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>550041</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6942830</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126057542</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>550036</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6942815</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126057561</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>549899</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6942773</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126057912</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>550006</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6942738</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126057607</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>549982</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6942703</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126057603</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>550002</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6942763</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>6 ex</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126057555</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97212</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>550012</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6942981</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126057550</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91682</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>550033</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6942796</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126057903</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>550023</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6942664</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126057887</v>
+      </c>
+      <c r="B32" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>550013</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6942905</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126057570</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>550078</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6942902</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126057936</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>549946</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6942691</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126057900</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>549962</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6942699</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126057940</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>550019</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6942882</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126057939</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Västanå-Grössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>549977</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6942721</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126057528</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kaffepannmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>550027</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6942798</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -2768,10 +2768,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057881</v>
+        <v>126057604</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,34 +2779,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550014</v>
+        <v>550077</v>
       </c>
       <c r="R20" t="n">
-        <v>6942905</v>
+        <v>6942975</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2839,11 +2839,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,10 +2865,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057604</v>
+        <v>126057881</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,34 +2876,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550077</v>
+        <v>550014</v>
       </c>
       <c r="R21" t="n">
-        <v>6942975</v>
+        <v>6942905</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2941,6 +2936,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3284,7 +3284,7 @@
         <v>126057561</v>
       </c>
       <c r="B25" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>126057607</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>126057603</v>
       </c>
       <c r="B28" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3679,32 +3679,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057555</v>
+        <v>126057550</v>
       </c>
       <c r="B29" t="n">
-        <v>97212</v>
+        <v>91686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550012</v>
+        <v>550033</v>
       </c>
       <c r="R29" t="n">
-        <v>6942981</v>
+        <v>6942796</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3776,45 +3776,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057550</v>
+        <v>126057903</v>
       </c>
       <c r="B30" t="n">
-        <v>91682</v>
+        <v>80075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550033</v>
+        <v>550023</v>
       </c>
       <c r="R30" t="n">
-        <v>6942796</v>
+        <v>6942664</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3873,32 +3873,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057903</v>
+        <v>126057887</v>
       </c>
       <c r="B31" t="n">
-        <v>80071</v>
+        <v>56843</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550023</v>
+        <v>550013</v>
       </c>
       <c r="R31" t="n">
-        <v>6942664</v>
+        <v>6942905</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3944,6 +3944,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,10 +3975,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057887</v>
+        <v>126057555</v>
       </c>
       <c r="B32" t="n">
-        <v>56843</v>
+        <v>97216</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,34 +3986,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550013</v>
+        <v>550012</v>
       </c>
       <c r="R32" t="n">
-        <v>6942905</v>
+        <v>6942981</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4041,11 +4046,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4072,10 +4072,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057570</v>
+        <v>126057936</v>
       </c>
       <c r="B33" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4083,34 +4083,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550078</v>
+        <v>549946</v>
       </c>
       <c r="R33" t="n">
-        <v>6942902</v>
+        <v>6942691</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4169,10 +4169,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057936</v>
+        <v>126057570</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4180,34 +4180,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549946</v>
+        <v>550078</v>
       </c>
       <c r="R34" t="n">
-        <v>6942691</v>
+        <v>6942902</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4269,7 +4269,7 @@
         <v>126057900</v>
       </c>
       <c r="B35" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>126057940</v>
       </c>
       <c r="B36" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>126057939</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126057528</v>
       </c>
       <c r="B38" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3580,7 +3580,7 @@
         <v>126057603</v>
       </c>
       <c r="B28" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3679,32 +3679,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057550</v>
+        <v>126057555</v>
       </c>
       <c r="B29" t="n">
-        <v>91686</v>
+        <v>97217</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550033</v>
+        <v>550012</v>
       </c>
       <c r="R29" t="n">
-        <v>6942796</v>
+        <v>6942981</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3776,45 +3776,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057903</v>
+        <v>126057550</v>
       </c>
       <c r="B30" t="n">
-        <v>80075</v>
+        <v>91686</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550023</v>
+        <v>550033</v>
       </c>
       <c r="R30" t="n">
-        <v>6942664</v>
+        <v>6942796</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3873,32 +3873,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057887</v>
+        <v>126057903</v>
       </c>
       <c r="B31" t="n">
-        <v>56843</v>
+        <v>80075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550013</v>
+        <v>550023</v>
       </c>
       <c r="R31" t="n">
-        <v>6942905</v>
+        <v>6942664</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3944,11 +3944,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3975,10 +3970,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057555</v>
+        <v>126057887</v>
       </c>
       <c r="B32" t="n">
-        <v>97216</v>
+        <v>56843</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,34 +3981,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550012</v>
+        <v>550013</v>
       </c>
       <c r="R32" t="n">
-        <v>6942981</v>
+        <v>6942905</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4046,6 +4041,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4169,10 +4169,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057570</v>
+        <v>126057940</v>
       </c>
       <c r="B34" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4180,34 +4180,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550078</v>
+        <v>550019</v>
       </c>
       <c r="R34" t="n">
-        <v>6942902</v>
+        <v>6942882</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4266,45 +4266,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057900</v>
+        <v>126057570</v>
       </c>
       <c r="B35" t="n">
-        <v>80103</v>
+        <v>80075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549962</v>
+        <v>550078</v>
       </c>
       <c r="R35" t="n">
-        <v>6942699</v>
+        <v>6942902</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4363,32 +4363,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057940</v>
+        <v>126057900</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>80103</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550019</v>
+        <v>549962</v>
       </c>
       <c r="R36" t="n">
-        <v>6942882</v>
+        <v>6942699</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3679,32 +3679,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057555</v>
+        <v>126057550</v>
       </c>
       <c r="B29" t="n">
-        <v>97217</v>
+        <v>91686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550012</v>
+        <v>550033</v>
       </c>
       <c r="R29" t="n">
-        <v>6942981</v>
+        <v>6942796</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3776,45 +3776,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057550</v>
+        <v>126057903</v>
       </c>
       <c r="B30" t="n">
-        <v>91686</v>
+        <v>80075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550033</v>
+        <v>550023</v>
       </c>
       <c r="R30" t="n">
-        <v>6942796</v>
+        <v>6942664</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3873,32 +3873,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057903</v>
+        <v>126057887</v>
       </c>
       <c r="B31" t="n">
-        <v>80075</v>
+        <v>56843</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550023</v>
+        <v>550013</v>
       </c>
       <c r="R31" t="n">
-        <v>6942664</v>
+        <v>6942905</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3944,6 +3944,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,10 +3975,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057887</v>
+        <v>126057555</v>
       </c>
       <c r="B32" t="n">
-        <v>56843</v>
+        <v>97217</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,34 +3986,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550013</v>
+        <v>550012</v>
       </c>
       <c r="R32" t="n">
-        <v>6942905</v>
+        <v>6942981</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4041,11 +4046,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -2768,10 +2768,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057604</v>
+        <v>126057881</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,34 +2779,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550077</v>
+        <v>550014</v>
       </c>
       <c r="R20" t="n">
-        <v>6942975</v>
+        <v>6942905</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2839,6 +2839,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2865,10 +2870,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057881</v>
+        <v>126057604</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,34 +2881,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550014</v>
+        <v>550077</v>
       </c>
       <c r="R21" t="n">
-        <v>6942905</v>
+        <v>6942975</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2936,11 +2941,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2970,7 +2970,7 @@
         <v>126057931</v>
       </c>
       <c r="B22" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,10 +3077,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057541</v>
+        <v>126057542</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550041</v>
+        <v>550036</v>
       </c>
       <c r="R23" t="n">
-        <v>6942830</v>
+        <v>6942815</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126057542</v>
+        <v>126057541</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550036</v>
+        <v>550041</v>
       </c>
       <c r="R24" t="n">
-        <v>6942815</v>
+        <v>6942830</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3284,7 +3284,7 @@
         <v>126057561</v>
       </c>
       <c r="B25" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>126057912</v>
       </c>
       <c r="B26" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>126057607</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>126057603</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3679,45 +3679,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057550</v>
+        <v>126057903</v>
       </c>
       <c r="B29" t="n">
-        <v>91686</v>
+        <v>80076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550033</v>
+        <v>550023</v>
       </c>
       <c r="R29" t="n">
-        <v>6942796</v>
+        <v>6942664</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3776,45 +3776,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057903</v>
+        <v>126057550</v>
       </c>
       <c r="B30" t="n">
-        <v>80075</v>
+        <v>91688</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550023</v>
+        <v>550033</v>
       </c>
       <c r="R30" t="n">
-        <v>6942664</v>
+        <v>6942796</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3876,7 +3876,7 @@
         <v>126057887</v>
       </c>
       <c r="B31" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>126057555</v>
       </c>
       <c r="B32" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>126057936</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4169,10 +4169,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057940</v>
+        <v>126057570</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4180,34 +4180,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550019</v>
+        <v>550078</v>
       </c>
       <c r="R34" t="n">
-        <v>6942882</v>
+        <v>6942902</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4266,10 +4266,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057570</v>
+        <v>126057940</v>
       </c>
       <c r="B35" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4277,34 +4277,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550078</v>
+        <v>550019</v>
       </c>
       <c r="R35" t="n">
-        <v>6942902</v>
+        <v>6942882</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4366,7 +4366,7 @@
         <v>126057900</v>
       </c>
       <c r="B36" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>126057939</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126057528</v>
       </c>
       <c r="B38" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3679,45 +3679,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057903</v>
+        <v>126057550</v>
       </c>
       <c r="B29" t="n">
-        <v>80076</v>
+        <v>91688</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550023</v>
+        <v>550033</v>
       </c>
       <c r="R29" t="n">
-        <v>6942664</v>
+        <v>6942796</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3776,32 +3776,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057550</v>
+        <v>126057555</v>
       </c>
       <c r="B30" t="n">
-        <v>91688</v>
+        <v>97219</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550033</v>
+        <v>550012</v>
       </c>
       <c r="R30" t="n">
-        <v>6942796</v>
+        <v>6942981</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3873,32 +3873,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057887</v>
+        <v>126057903</v>
       </c>
       <c r="B31" t="n">
-        <v>56844</v>
+        <v>80076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550013</v>
+        <v>550023</v>
       </c>
       <c r="R31" t="n">
-        <v>6942905</v>
+        <v>6942664</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3944,11 +3944,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3975,10 +3970,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057555</v>
+        <v>126057887</v>
       </c>
       <c r="B32" t="n">
-        <v>97219</v>
+        <v>56844</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,34 +3981,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550012</v>
+        <v>550013</v>
       </c>
       <c r="R32" t="n">
-        <v>6942981</v>
+        <v>6942905</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4046,6 +4041,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -2768,10 +2768,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057881</v>
+        <v>126057604</v>
       </c>
       <c r="B20" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,34 +2779,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550014</v>
+        <v>550077</v>
       </c>
       <c r="R20" t="n">
-        <v>6942905</v>
+        <v>6942975</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2839,11 +2839,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,10 +2865,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057604</v>
+        <v>126057881</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,34 +2876,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550077</v>
+        <v>550014</v>
       </c>
       <c r="R21" t="n">
-        <v>6942975</v>
+        <v>6942905</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2941,6 +2936,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3077,7 +3077,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126057542</v>
+        <v>126057541</v>
       </c>
       <c r="B23" t="n">
         <v>57652</v>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550036</v>
+        <v>550041</v>
       </c>
       <c r="R23" t="n">
-        <v>6942815</v>
+        <v>6942830</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3179,7 +3179,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126057541</v>
+        <v>126057542</v>
       </c>
       <c r="B24" t="n">
         <v>57652</v>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550041</v>
+        <v>550036</v>
       </c>
       <c r="R24" t="n">
-        <v>6942830</v>
+        <v>6942815</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3580,7 +3580,7 @@
         <v>126057603</v>
       </c>
       <c r="B28" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3679,45 +3679,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057550</v>
+        <v>126057887</v>
       </c>
       <c r="B29" t="n">
-        <v>91688</v>
+        <v>56844</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550033</v>
+        <v>550013</v>
       </c>
       <c r="R29" t="n">
-        <v>6942796</v>
+        <v>6942905</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3750,6 +3750,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3779,7 +3784,7 @@
         <v>126057555</v>
       </c>
       <c r="B30" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3970,45 +3975,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057887</v>
+        <v>126057550</v>
       </c>
       <c r="B32" t="n">
-        <v>56844</v>
+        <v>91690</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550013</v>
+        <v>550033</v>
       </c>
       <c r="R32" t="n">
-        <v>6942905</v>
+        <v>6942796</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4041,11 +4046,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4266,32 +4266,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057940</v>
+        <v>126057900</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>80104</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550019</v>
+        <v>549962</v>
       </c>
       <c r="R35" t="n">
-        <v>6942882</v>
+        <v>6942699</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4363,32 +4363,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057900</v>
+        <v>126057940</v>
       </c>
       <c r="B36" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549962</v>
+        <v>550019</v>
       </c>
       <c r="R36" t="n">
-        <v>6942699</v>
+        <v>6942882</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4560,7 +4560,7 @@
         <v>126057528</v>
       </c>
       <c r="B38" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3781,32 +3781,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057555</v>
+        <v>126057550</v>
       </c>
       <c r="B30" t="n">
-        <v>97221</v>
+        <v>91690</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550012</v>
+        <v>550033</v>
       </c>
       <c r="R30" t="n">
-        <v>6942981</v>
+        <v>6942796</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3975,32 +3975,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057550</v>
+        <v>126057555</v>
       </c>
       <c r="B32" t="n">
-        <v>91690</v>
+        <v>97221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550033</v>
+        <v>550012</v>
       </c>
       <c r="R32" t="n">
-        <v>6942796</v>
+        <v>6942981</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4072,10 +4072,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057936</v>
+        <v>126057570</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4083,34 +4083,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549946</v>
+        <v>550078</v>
       </c>
       <c r="R33" t="n">
-        <v>6942691</v>
+        <v>6942902</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4169,45 +4169,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057570</v>
+        <v>126057900</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>80104</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550078</v>
+        <v>549962</v>
       </c>
       <c r="R34" t="n">
-        <v>6942902</v>
+        <v>6942699</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4266,32 +4266,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057900</v>
+        <v>126057940</v>
       </c>
       <c r="B35" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549962</v>
+        <v>550019</v>
       </c>
       <c r="R35" t="n">
-        <v>6942699</v>
+        <v>6942882</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057940</v>
+        <v>126057936</v>
       </c>
       <c r="B36" t="n">
         <v>78973</v>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550019</v>
+        <v>549946</v>
       </c>
       <c r="R36" t="n">
-        <v>6942882</v>
+        <v>6942691</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3580,7 +3580,7 @@
         <v>126057603</v>
       </c>
       <c r="B28" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3679,32 +3679,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057887</v>
+        <v>126057903</v>
       </c>
       <c r="B29" t="n">
-        <v>56844</v>
+        <v>80076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550013</v>
+        <v>550023</v>
       </c>
       <c r="R29" t="n">
-        <v>6942905</v>
+        <v>6942664</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3750,11 +3750,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3781,45 +3776,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057550</v>
+        <v>126057887</v>
       </c>
       <c r="B30" t="n">
-        <v>91690</v>
+        <v>56844</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550033</v>
+        <v>550013</v>
       </c>
       <c r="R30" t="n">
-        <v>6942796</v>
+        <v>6942905</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3852,6 +3847,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3878,45 +3878,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057903</v>
+        <v>126057550</v>
       </c>
       <c r="B31" t="n">
-        <v>80076</v>
+        <v>91692</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550023</v>
+        <v>550033</v>
       </c>
       <c r="R31" t="n">
-        <v>6942664</v>
+        <v>6942796</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3978,7 +3978,7 @@
         <v>126057555</v>
       </c>
       <c r="B32" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,10 +4072,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057570</v>
+        <v>126057936</v>
       </c>
       <c r="B33" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4083,34 +4083,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550078</v>
+        <v>549946</v>
       </c>
       <c r="R33" t="n">
-        <v>6942902</v>
+        <v>6942691</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4169,45 +4169,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057900</v>
+        <v>126057570</v>
       </c>
       <c r="B34" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549962</v>
+        <v>550078</v>
       </c>
       <c r="R34" t="n">
-        <v>6942699</v>
+        <v>6942902</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4266,32 +4266,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057940</v>
+        <v>126057900</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>80104</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550019</v>
+        <v>549962</v>
       </c>
       <c r="R35" t="n">
-        <v>6942882</v>
+        <v>6942699</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057936</v>
+        <v>126057940</v>
       </c>
       <c r="B36" t="n">
         <v>78973</v>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549946</v>
+        <v>550019</v>
       </c>
       <c r="R36" t="n">
-        <v>6942691</v>
+        <v>6942882</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4560,7 +4560,7 @@
         <v>126057528</v>
       </c>
       <c r="B38" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -2771,7 +2771,7 @@
         <v>126057604</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>126057881</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>126057931</v>
       </c>
       <c r="B22" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>126057541</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>126057542</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>126057561</v>
       </c>
       <c r="B25" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>126057912</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>126057607</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>126057603</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3679,45 +3679,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057903</v>
+        <v>126057550</v>
       </c>
       <c r="B29" t="n">
-        <v>80076</v>
+        <v>91696</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550023</v>
+        <v>550033</v>
       </c>
       <c r="R29" t="n">
-        <v>6942664</v>
+        <v>6942796</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3776,32 +3776,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057887</v>
+        <v>126057903</v>
       </c>
       <c r="B30" t="n">
-        <v>56844</v>
+        <v>80080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550013</v>
+        <v>550023</v>
       </c>
       <c r="R30" t="n">
-        <v>6942905</v>
+        <v>6942664</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3847,11 +3847,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3878,45 +3873,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057550</v>
+        <v>126057887</v>
       </c>
       <c r="B31" t="n">
-        <v>91692</v>
+        <v>56848</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550033</v>
+        <v>550013</v>
       </c>
       <c r="R31" t="n">
-        <v>6942796</v>
+        <v>6942905</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3949,6 +3944,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3978,7 +3978,7 @@
         <v>126057555</v>
       </c>
       <c r="B32" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>126057936</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>126057570</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>126057900</v>
       </c>
       <c r="B35" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>126057940</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>126057939</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126057528</v>
       </c>
       <c r="B38" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3679,32 +3679,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057550</v>
+        <v>126057555</v>
       </c>
       <c r="B29" t="n">
-        <v>91696</v>
+        <v>97227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550033</v>
+        <v>550012</v>
       </c>
       <c r="R29" t="n">
-        <v>6942796</v>
+        <v>6942981</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3776,45 +3776,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057903</v>
+        <v>126057550</v>
       </c>
       <c r="B30" t="n">
-        <v>80080</v>
+        <v>91696</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550023</v>
+        <v>550033</v>
       </c>
       <c r="R30" t="n">
-        <v>6942664</v>
+        <v>6942796</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3975,45 +3975,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057555</v>
+        <v>126057903</v>
       </c>
       <c r="B32" t="n">
-        <v>97227</v>
+        <v>80080</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550012</v>
+        <v>550023</v>
       </c>
       <c r="R32" t="n">
-        <v>6942981</v>
+        <v>6942664</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3580,7 +3580,7 @@
         <v>126057603</v>
       </c>
       <c r="B28" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3679,32 +3679,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057555</v>
+        <v>126057550</v>
       </c>
       <c r="B29" t="n">
-        <v>97227</v>
+        <v>91696</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550012</v>
+        <v>550033</v>
       </c>
       <c r="R29" t="n">
-        <v>6942981</v>
+        <v>6942796</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3776,45 +3776,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057550</v>
+        <v>126057887</v>
       </c>
       <c r="B30" t="n">
-        <v>91696</v>
+        <v>56848</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550033</v>
+        <v>550013</v>
       </c>
       <c r="R30" t="n">
-        <v>6942796</v>
+        <v>6942905</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3847,6 +3847,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3873,32 +3878,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057887</v>
+        <v>126057903</v>
       </c>
       <c r="B31" t="n">
-        <v>56848</v>
+        <v>80080</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3908,10 +3913,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550013</v>
+        <v>550023</v>
       </c>
       <c r="R31" t="n">
-        <v>6942905</v>
+        <v>6942664</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3944,11 +3949,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3975,45 +3975,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057903</v>
+        <v>126057555</v>
       </c>
       <c r="B32" t="n">
-        <v>80080</v>
+        <v>97230</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550023</v>
+        <v>550012</v>
       </c>
       <c r="R32" t="n">
-        <v>6942664</v>
+        <v>6942981</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4072,10 +4072,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057936</v>
+        <v>126057570</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4083,34 +4083,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549946</v>
+        <v>550078</v>
       </c>
       <c r="R33" t="n">
-        <v>6942691</v>
+        <v>6942902</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4169,45 +4169,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057570</v>
+        <v>126057900</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>80108</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550078</v>
+        <v>549962</v>
       </c>
       <c r="R34" t="n">
-        <v>6942902</v>
+        <v>6942699</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4266,32 +4266,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057900</v>
+        <v>126057936</v>
       </c>
       <c r="B35" t="n">
-        <v>80108</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549962</v>
+        <v>549946</v>
       </c>
       <c r="R35" t="n">
-        <v>6942699</v>
+        <v>6942691</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3679,45 +3679,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057550</v>
+        <v>126057903</v>
       </c>
       <c r="B29" t="n">
-        <v>91696</v>
+        <v>80080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550033</v>
+        <v>550023</v>
       </c>
       <c r="R29" t="n">
-        <v>6942796</v>
+        <v>6942664</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057887</v>
+        <v>126057555</v>
       </c>
       <c r="B30" t="n">
-        <v>56848</v>
+        <v>97230</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,34 +3787,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550013</v>
+        <v>550012</v>
       </c>
       <c r="R30" t="n">
-        <v>6942905</v>
+        <v>6942981</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3847,11 +3847,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3878,45 +3873,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057903</v>
+        <v>126057550</v>
       </c>
       <c r="B31" t="n">
-        <v>80080</v>
+        <v>91696</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550023</v>
+        <v>550033</v>
       </c>
       <c r="R31" t="n">
-        <v>6942664</v>
+        <v>6942796</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3975,10 +3970,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057555</v>
+        <v>126057887</v>
       </c>
       <c r="B32" t="n">
-        <v>97230</v>
+        <v>56848</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,34 +3981,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550012</v>
+        <v>550013</v>
       </c>
       <c r="R32" t="n">
-        <v>6942981</v>
+        <v>6942905</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4046,6 +4041,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3776,32 +3776,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057555</v>
+        <v>126057550</v>
       </c>
       <c r="B30" t="n">
-        <v>97230</v>
+        <v>91696</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550012</v>
+        <v>550033</v>
       </c>
       <c r="R30" t="n">
-        <v>6942981</v>
+        <v>6942796</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3873,45 +3873,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057550</v>
+        <v>126057887</v>
       </c>
       <c r="B31" t="n">
-        <v>91696</v>
+        <v>56848</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550033</v>
+        <v>550013</v>
       </c>
       <c r="R31" t="n">
-        <v>6942796</v>
+        <v>6942905</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3944,6 +3944,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,10 +3975,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057887</v>
+        <v>126057555</v>
       </c>
       <c r="B32" t="n">
-        <v>56848</v>
+        <v>97230</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,34 +3986,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550013</v>
+        <v>550012</v>
       </c>
       <c r="R32" t="n">
-        <v>6942905</v>
+        <v>6942981</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4041,11 +4046,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4266,7 +4266,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057936</v>
+        <v>126057940</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549946</v>
+        <v>550019</v>
       </c>
       <c r="R35" t="n">
-        <v>6942691</v>
+        <v>6942882</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057940</v>
+        <v>126057936</v>
       </c>
       <c r="B36" t="n">
         <v>78977</v>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550019</v>
+        <v>549946</v>
       </c>
       <c r="R36" t="n">
-        <v>6942882</v>
+        <v>6942691</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3679,45 +3679,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057903</v>
+        <v>126057550</v>
       </c>
       <c r="B29" t="n">
-        <v>80080</v>
+        <v>91696</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550023</v>
+        <v>550033</v>
       </c>
       <c r="R29" t="n">
-        <v>6942664</v>
+        <v>6942796</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3776,45 +3776,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057550</v>
+        <v>126057887</v>
       </c>
       <c r="B30" t="n">
-        <v>91696</v>
+        <v>56848</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550033</v>
+        <v>550013</v>
       </c>
       <c r="R30" t="n">
-        <v>6942796</v>
+        <v>6942905</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3847,6 +3847,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3873,10 +3878,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057887</v>
+        <v>126057555</v>
       </c>
       <c r="B31" t="n">
-        <v>56848</v>
+        <v>97230</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3884,34 +3889,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550013</v>
+        <v>550012</v>
       </c>
       <c r="R31" t="n">
-        <v>6942905</v>
+        <v>6942981</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3944,11 +3949,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3975,45 +3975,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057555</v>
+        <v>126057903</v>
       </c>
       <c r="B32" t="n">
-        <v>97230</v>
+        <v>80080</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550012</v>
+        <v>550023</v>
       </c>
       <c r="R32" t="n">
-        <v>6942981</v>
+        <v>6942664</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4072,10 +4072,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126057570</v>
+        <v>126057936</v>
       </c>
       <c r="B33" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4083,34 +4083,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550078</v>
+        <v>549946</v>
       </c>
       <c r="R33" t="n">
-        <v>6942902</v>
+        <v>6942691</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4169,45 +4169,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057900</v>
+        <v>126057570</v>
       </c>
       <c r="B34" t="n">
-        <v>80108</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549962</v>
+        <v>550078</v>
       </c>
       <c r="R34" t="n">
-        <v>6942699</v>
+        <v>6942902</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4266,32 +4266,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057940</v>
+        <v>126057900</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>80108</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550019</v>
+        <v>549962</v>
       </c>
       <c r="R35" t="n">
-        <v>6942882</v>
+        <v>6942699</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057936</v>
+        <v>126057940</v>
       </c>
       <c r="B36" t="n">
         <v>78977</v>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>549946</v>
+        <v>550019</v>
       </c>
       <c r="R36" t="n">
-        <v>6942691</v>
+        <v>6942882</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -2771,7 +2771,7 @@
         <v>126057604</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>126057881</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>126057931</v>
       </c>
       <c r="B22" t="n">
-        <v>56839</v>
+        <v>56840</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>126057541</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>126057542</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>126057561</v>
       </c>
       <c r="B25" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>126057912</v>
       </c>
       <c r="B26" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>126057607</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>126057603</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3679,45 +3679,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057550</v>
+        <v>126057887</v>
       </c>
       <c r="B29" t="n">
-        <v>91696</v>
+        <v>56849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550033</v>
+        <v>550013</v>
       </c>
       <c r="R29" t="n">
-        <v>6942796</v>
+        <v>6942905</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3750,6 +3750,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3776,45 +3781,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057887</v>
+        <v>126057550</v>
       </c>
       <c r="B30" t="n">
-        <v>56848</v>
+        <v>91699</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550013</v>
+        <v>550033</v>
       </c>
       <c r="R30" t="n">
-        <v>6942905</v>
+        <v>6942796</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3847,11 +3852,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3878,45 +3878,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057555</v>
+        <v>126057903</v>
       </c>
       <c r="B31" t="n">
-        <v>97230</v>
+        <v>80083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550012</v>
+        <v>550023</v>
       </c>
       <c r="R31" t="n">
-        <v>6942981</v>
+        <v>6942664</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3975,45 +3975,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057903</v>
+        <v>126057555</v>
       </c>
       <c r="B32" t="n">
-        <v>80080</v>
+        <v>97239</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550023</v>
+        <v>550012</v>
       </c>
       <c r="R32" t="n">
-        <v>6942664</v>
+        <v>6942981</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4075,7 +4075,7 @@
         <v>126057936</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>126057570</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>126057900</v>
       </c>
       <c r="B35" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>126057940</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>126057939</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126057528</v>
       </c>
       <c r="B38" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3679,45 +3679,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057887</v>
+        <v>126057550</v>
       </c>
       <c r="B29" t="n">
-        <v>56849</v>
+        <v>91699</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550013</v>
+        <v>550033</v>
       </c>
       <c r="R29" t="n">
-        <v>6942905</v>
+        <v>6942796</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3750,11 +3750,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3781,45 +3776,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057550</v>
+        <v>126057903</v>
       </c>
       <c r="B30" t="n">
-        <v>91699</v>
+        <v>80083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550033</v>
+        <v>550023</v>
       </c>
       <c r="R30" t="n">
-        <v>6942796</v>
+        <v>6942664</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3878,32 +3873,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057903</v>
+        <v>126057887</v>
       </c>
       <c r="B31" t="n">
-        <v>80083</v>
+        <v>56849</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3913,10 +3908,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550023</v>
+        <v>550013</v>
       </c>
       <c r="R31" t="n">
-        <v>6942664</v>
+        <v>6942905</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3949,6 +3944,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -2768,10 +2768,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057604</v>
+        <v>126057881</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,34 +2779,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550077</v>
+        <v>550014</v>
       </c>
       <c r="R20" t="n">
-        <v>6942975</v>
+        <v>6942905</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2839,6 +2839,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2865,10 +2870,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057881</v>
+        <v>126057604</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,34 +2881,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550014</v>
+        <v>550077</v>
       </c>
       <c r="R21" t="n">
-        <v>6942905</v>
+        <v>6942975</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2936,11 +2941,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3679,45 +3679,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057550</v>
+        <v>126057887</v>
       </c>
       <c r="B29" t="n">
-        <v>91699</v>
+        <v>56849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550033</v>
+        <v>550013</v>
       </c>
       <c r="R29" t="n">
-        <v>6942796</v>
+        <v>6942905</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3750,6 +3750,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3873,45 +3878,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057887</v>
+        <v>126057550</v>
       </c>
       <c r="B31" t="n">
-        <v>56849</v>
+        <v>91699</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550013</v>
+        <v>550033</v>
       </c>
       <c r="R31" t="n">
-        <v>6942905</v>
+        <v>6942796</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3944,11 +3949,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4169,10 +4169,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126057570</v>
+        <v>126057940</v>
       </c>
       <c r="B34" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4180,34 +4180,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550078</v>
+        <v>550019</v>
       </c>
       <c r="R34" t="n">
-        <v>6942902</v>
+        <v>6942882</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4266,45 +4266,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057900</v>
+        <v>126057570</v>
       </c>
       <c r="B35" t="n">
-        <v>80111</v>
+        <v>80083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549962</v>
+        <v>550078</v>
       </c>
       <c r="R35" t="n">
-        <v>6942699</v>
+        <v>6942902</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4363,32 +4363,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057940</v>
+        <v>126057900</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>80111</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4398,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550019</v>
+        <v>549962</v>
       </c>
       <c r="R36" t="n">
-        <v>6942882</v>
+        <v>6942699</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3781,45 +3781,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057903</v>
+        <v>126057555</v>
       </c>
       <c r="B30" t="n">
-        <v>80083</v>
+        <v>97239</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550023</v>
+        <v>550012</v>
       </c>
       <c r="R30" t="n">
-        <v>6942664</v>
+        <v>6942981</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3878,45 +3878,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057550</v>
+        <v>126057903</v>
       </c>
       <c r="B31" t="n">
-        <v>91699</v>
+        <v>80083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550033</v>
+        <v>550023</v>
       </c>
       <c r="R31" t="n">
-        <v>6942796</v>
+        <v>6942664</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3975,32 +3975,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057555</v>
+        <v>126057550</v>
       </c>
       <c r="B32" t="n">
-        <v>97239</v>
+        <v>91699</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550012</v>
+        <v>550033</v>
       </c>
       <c r="R32" t="n">
-        <v>6942981</v>
+        <v>6942796</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -3781,45 +3781,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057555</v>
+        <v>126057903</v>
       </c>
       <c r="B30" t="n">
-        <v>97239</v>
+        <v>80083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550012</v>
+        <v>550023</v>
       </c>
       <c r="R30" t="n">
-        <v>6942981</v>
+        <v>6942664</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3878,45 +3878,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057903</v>
+        <v>126057550</v>
       </c>
       <c r="B31" t="n">
-        <v>80083</v>
+        <v>91699</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550023</v>
+        <v>550033</v>
       </c>
       <c r="R31" t="n">
-        <v>6942664</v>
+        <v>6942796</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3975,32 +3975,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057550</v>
+        <v>126057555</v>
       </c>
       <c r="B32" t="n">
-        <v>91699</v>
+        <v>97239</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550033</v>
+        <v>550012</v>
       </c>
       <c r="R32" t="n">
-        <v>6942796</v>
+        <v>6942981</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -2768,10 +2768,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126057881</v>
+        <v>126057604</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,34 +2779,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550014</v>
+        <v>550077</v>
       </c>
       <c r="R20" t="n">
-        <v>6942905</v>
+        <v>6942975</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2839,11 +2839,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,10 +2865,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126057604</v>
+        <v>126057881</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,34 +2876,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550077</v>
+        <v>550014</v>
       </c>
       <c r="R21" t="n">
-        <v>6942975</v>
+        <v>6942905</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2941,6 +2936,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3781,45 +3781,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057903</v>
+        <v>126057555</v>
       </c>
       <c r="B30" t="n">
-        <v>80083</v>
+        <v>97239</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västanå-Grössjön, Mpd</t>
+          <t>Kaffepannmyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550023</v>
+        <v>550012</v>
       </c>
       <c r="R30" t="n">
-        <v>6942664</v>
+        <v>6942981</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3878,45 +3878,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126057550</v>
+        <v>126057903</v>
       </c>
       <c r="B31" t="n">
-        <v>91699</v>
+        <v>80083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kaffepannmyran, Mpd</t>
+          <t>Västanå-Grössjön, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550033</v>
+        <v>550023</v>
       </c>
       <c r="R31" t="n">
-        <v>6942796</v>
+        <v>6942664</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3975,32 +3975,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126057555</v>
+        <v>126057550</v>
       </c>
       <c r="B32" t="n">
-        <v>97239</v>
+        <v>91699</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550012</v>
+        <v>550033</v>
       </c>
       <c r="R32" t="n">
-        <v>6942981</v>
+        <v>6942796</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 23626-2025 artfynd.xlsx
+++ b/artfynd/A 23626-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057528</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057550</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997577</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997093</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997094</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997095</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997623</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996910</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1578,6 +1623,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997410</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1679,6 +1729,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997442</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1780,6 +1835,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997443</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997444</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1982,6 +2047,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997445</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2083,6 +2153,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997446</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2180,6 +2255,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057604</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2282,6 +2362,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057607</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2379,6 +2464,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057936</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2476,6 +2566,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057939</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2573,6 +2668,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057940</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2674,6 +2774,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996917</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2771,6 +2876,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057579</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2872,6 +2982,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997125</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2973,6 +3088,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997236</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3070,6 +3190,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057570</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3167,6 +3292,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057903</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3264,6 +3394,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057904</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3361,6 +3496,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057896</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3458,6 +3598,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057898</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3555,6 +3700,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057900</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3656,6 +3806,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997695</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3757,6 +3912,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997277</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3859,6 +4019,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057384</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3961,6 +4126,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057541</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4063,6 +4233,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057542</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4165,6 +4340,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057881</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4267,6 +4447,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057887</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4377,6 +4562,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057931</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4474,6 +4664,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057912</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4575,6 +4770,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997307</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4677,6 +4877,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057603</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4774,6 +4979,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057555</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4871,6 +5081,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057561</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4972,8 +5187,58 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997323</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>